--- a/data/memories/memory_01/locales/es/documents/archive/Document Access Log.xlsx
+++ b/data/memories/memory_01/locales/es/documents/archive/Document Access Log.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Document Access Log</t>
+          <t>Registro de acceso a documentos</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,48 +469,48 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Administración</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Recent Access Records</t>
+          <t>Registros de acceso recientes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Usuario</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Acción</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12 September</t>
+          <t>12 de septiembre</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Historical Records</t>
+          <t>Registros históricos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -520,19 +520,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Viewed</t>
+          <t>Visto</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13 September</t>
+          <t>13 de septiembre</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Organisation Chart Old</t>
+          <t>organigrama antiguo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -542,19 +542,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Copied</t>
+          <t>copiado</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14 September</t>
+          <t>14 de septiembre</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Employee Registry Previous</t>
+          <t>Registro de Empleados Anterior</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -564,14 +564,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Viewed</t>
+          <t>Visto</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Historical documents are subject to restricted access. Original records must not be removed without authorisation.</t>
+          <t>Los documentos históricos están sujetos a acceso restringido. Los registros originales no deben eliminarse sin autorización.</t>
         </is>
       </c>
     </row>
